--- a/data/out/variants/v4_no_fuel_consumption_lags/summary_v4_no_fuel_consumption_lags.xlsx
+++ b/data/out/variants/v4_no_fuel_consumption_lags/summary_v4_no_fuel_consumption_lags.xlsx
@@ -523,19 +523,19 @@
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>0.9466617382894909</v>
+        <v>0.9466617382894907</v>
       </c>
       <c r="F2" t="n">
-        <v>47.03474640717087</v>
+        <v>47.03474640717103</v>
       </c>
       <c r="G2" t="n">
-        <v>13410.16675944592</v>
+        <v>13410.16675944593</v>
       </c>
       <c r="H2" t="n">
-        <v>115.8022744139592</v>
+        <v>115.8022744139593</v>
       </c>
       <c r="I2" t="n">
-        <v>11.56378749039999</v>
+        <v>11.56378749039996</v>
       </c>
       <c r="J2" t="n">
         <v>48168</v>
@@ -547,7 +547,7 @@
         <v>9634</v>
       </c>
       <c r="M2" t="n">
-        <v>0.07653236389160156</v>
+        <v>0.08303689956665039</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -574,19 +574,19 @@
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>0.9466592220878717</v>
+        <v>0.9466592092883155</v>
       </c>
       <c r="F3" t="n">
-        <v>47.04723957449883</v>
+        <v>47.04726056088283</v>
       </c>
       <c r="G3" t="n">
-        <v>13410.79937629977</v>
+        <v>13410.80259433082</v>
       </c>
       <c r="H3" t="n">
-        <v>115.8050058343756</v>
+        <v>115.8050197285542</v>
       </c>
       <c r="I3" t="n">
-        <v>11.56647463978707</v>
+        <v>11.56648585695849</v>
       </c>
       <c r="J3" t="n">
         <v>48168</v>
@@ -598,7 +598,7 @@
         <v>9634</v>
       </c>
       <c r="M3" t="n">
-        <v>0.06160998344421387</v>
+        <v>0.06222224235534668</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -625,19 +625,19 @@
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>0.9467878048333025</v>
+        <v>0.9467794280504229</v>
       </c>
       <c r="F4" t="n">
-        <v>46.44331800172792</v>
+        <v>46.49099642086114</v>
       </c>
       <c r="G4" t="n">
-        <v>13378.4714375309</v>
+        <v>13380.57750645254</v>
       </c>
       <c r="H4" t="n">
-        <v>115.6653424217077</v>
+        <v>115.6744462119985</v>
       </c>
       <c r="I4" t="n">
-        <v>11.33870926155511</v>
+        <v>11.36115433844559</v>
       </c>
       <c r="J4" t="n">
         <v>48168</v>
@@ -649,7 +649,7 @@
         <v>9634</v>
       </c>
       <c r="M4" t="n">
-        <v>1.910881280899048</v>
+        <v>3.232712030410767</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -680,19 +680,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.9465486487041241</v>
+        <v>0.946547128559959</v>
       </c>
       <c r="F5" t="n">
-        <v>47.47305399118726</v>
+        <v>47.47597648227161</v>
       </c>
       <c r="G5" t="n">
-        <v>13438.59944828672</v>
+        <v>13438.98163897121</v>
       </c>
       <c r="H5" t="n">
-        <v>115.924973359008</v>
+        <v>115.9266217871081</v>
       </c>
       <c r="I5" t="n">
-        <v>11.64345258997241</v>
+        <v>11.64508399654649</v>
       </c>
       <c r="J5" t="n">
         <v>48168</v>
@@ -704,7 +704,7 @@
         <v>9634</v>
       </c>
       <c r="M5" t="n">
-        <v>17.95088148117065</v>
+        <v>41.30871176719666</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>-38.76869156318074</v>
+        <v>-38.77083192549562</v>
       </c>
     </row>
     <row r="6">
@@ -740,7 +740,7 @@
         <v>0.8414632613956305</v>
       </c>
       <c r="F6" t="n">
-        <v>74.49491854489349</v>
+        <v>74.49491854489348</v>
       </c>
       <c r="G6" t="n">
         <v>39858.89367227723</v>
@@ -761,7 +761,7 @@
         <v>9634</v>
       </c>
       <c r="M6" t="n">
-        <v>3.418932437896729</v>
+        <v>8.184883832931519</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>-73.1402855563076</v>
+        <v>-73.49935101914191</v>
       </c>
     </row>
     <row r="7">
@@ -794,19 +794,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.8155794772490637</v>
+        <v>0.8149852793167554</v>
       </c>
       <c r="F7" t="n">
-        <v>76.10510821127481</v>
+        <v>76.1385181990626</v>
       </c>
       <c r="G7" t="n">
-        <v>46366.52722911989</v>
+        <v>46515.91892477768</v>
       </c>
       <c r="H7" t="n">
-        <v>215.3288815489457</v>
+        <v>215.6754944929481</v>
       </c>
       <c r="I7" t="n">
-        <v>11.45009716275591</v>
+        <v>11.44785258400782</v>
       </c>
       <c r="J7" t="n">
         <v>48168</v>
@@ -818,7 +818,7 @@
         <v>9634</v>
       </c>
       <c r="M7" t="n">
-        <v>1587.545357465744</v>
+        <v>3706.700577259064</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>-78.10213392286086</v>
+        <v>-78.11792279539291</v>
       </c>
     </row>
     <row r="8">
@@ -847,23 +847,23 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.01, 'max_depth': 3, 'n_estimators': 500}</t>
+          <t>{'learning_rate': 0.05, 'max_depth': 3, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.6843937840774243</v>
+        <v>0.6784328417114158</v>
       </c>
       <c r="F8" t="n">
-        <v>94.76839151462418</v>
+        <v>95.6848862283138</v>
       </c>
       <c r="G8" t="n">
-        <v>79348.89233567848</v>
+        <v>80847.57693109098</v>
       </c>
       <c r="H8" t="n">
-        <v>281.6893543172665</v>
+        <v>284.337083285123</v>
       </c>
       <c r="I8" t="n">
-        <v>12.69379011092339</v>
+        <v>12.76438662923513</v>
       </c>
       <c r="J8" t="n">
         <v>48168</v>
@@ -875,7 +875,7 @@
         <v>9634</v>
       </c>
       <c r="M8" t="n">
-        <v>1991.326003313065</v>
+        <v>1641.479731798172</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>-74.5027732938904</v>
+        <v>-74.2572142438549</v>
       </c>
     </row>
     <row r="9">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.2280145229309428</v>
+        <v>0.2254452266996253</v>
       </c>
       <c r="F9" t="n">
-        <v>206.5139799992913</v>
+        <v>207.8417158895214</v>
       </c>
       <c r="G9" t="n">
-        <v>194090.576846203</v>
+        <v>194736.5426090804</v>
       </c>
       <c r="H9" t="n">
-        <v>440.5571209800189</v>
+        <v>441.289635737211</v>
       </c>
       <c r="I9" t="n">
-        <v>45.43186557089434</v>
+        <v>45.93080446821637</v>
       </c>
       <c r="J9" t="n">
         <v>48168</v>
@@ -932,7 +932,7 @@
         <v>9634</v>
       </c>
       <c r="M9" t="n">
-        <v>740.3249232769012</v>
+        <v>532.973833322525</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>-205.1026694579582</v>
+        <v>-205.2050290920366</v>
       </c>
     </row>
     <row r="10">
@@ -965,19 +965,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.7476071232343544</v>
+        <v>0.7459639002550571</v>
       </c>
       <c r="F10" t="n">
-        <v>134.1670973338474</v>
+        <v>135.7566179305436</v>
       </c>
       <c r="G10" t="n">
-        <v>63455.95933916083</v>
+        <v>63869.09417836744</v>
       </c>
       <c r="H10" t="n">
-        <v>251.9046631945523</v>
+        <v>252.7233550314799</v>
       </c>
       <c r="I10" t="n">
-        <v>35.60262205381895</v>
+        <v>35.79632170552165</v>
       </c>
       <c r="J10" t="n">
         <v>48168</v>
@@ -989,7 +989,7 @@
         <v>9634</v>
       </c>
       <c r="M10" t="n">
-        <v>7.944425344467163</v>
+        <v>6.8534996509552</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>-108.8784885547987</v>
+        <v>-109.1798464836125</v>
       </c>
     </row>
     <row r="11">
@@ -1018,23 +1018,23 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>{'n_estimators': 527, 'learning_rate': 0.018796609678191915, 'max_depth': 3, 'subsample': 0.7880439509791061, 'colsample_bytree': 0.8660785454386182}</t>
+          <t>{'n_estimators': 707, 'learning_rate': 0.02192119225162337, 'max_depth': 3, 'subsample': 0.6285806616176327, 'colsample_bytree': 0.846908125321739}</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.8087104434680485</v>
+        <v>0.8064910254293041</v>
       </c>
       <c r="F11" t="n">
-        <v>78.76837031514313</v>
+        <v>79.60354367183901</v>
       </c>
       <c r="G11" t="n">
-        <v>48093.52180160199</v>
+        <v>48651.52210108723</v>
       </c>
       <c r="H11" t="n">
-        <v>219.3023524762149</v>
+        <v>220.5709003950595</v>
       </c>
       <c r="I11" t="n">
-        <v>11.99017326458047</v>
+        <v>12.10100878758067</v>
       </c>
       <c r="J11" t="n">
         <v>48168</v>
@@ -1046,7 +1046,7 @@
         <v>9634</v>
       </c>
       <c r="M11" t="n">
-        <v>327.3317263126373</v>
+        <v>292.0308375358582</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1073,23 +1073,23 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>{'n_estimators': 688, 'learning_rate': 0.010070088601151708, 'num_leaves': 93, 'min_child_samples': 40}</t>
+          <t>{'n_estimators': 552, 'learning_rate': 0.012256404304997498, 'num_leaves': 103, 'min_child_samples': 49}</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.7803362463738426</v>
+        <v>0.8041347463274406</v>
       </c>
       <c r="F12" t="n">
-        <v>83.34352593454226</v>
+        <v>79.36108458689893</v>
       </c>
       <c r="G12" t="n">
-        <v>55227.28849170989</v>
+        <v>49243.93165240112</v>
       </c>
       <c r="H12" t="n">
-        <v>235.0048690808552</v>
+        <v>221.9097376241095</v>
       </c>
       <c r="I12" t="n">
-        <v>11.58595207230818</v>
+        <v>11.35053068916435</v>
       </c>
       <c r="J12" t="n">
         <v>48168</v>
@@ -1101,7 +1101,7 @@
         <v>9634</v>
       </c>
       <c r="M12" t="n">
-        <v>874.1021618843079</v>
+        <v>571.9427638053894</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1128,23 +1128,23 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>{'iterations': 602, 'learning_rate': 0.03629300608161893, 'depth': 4}</t>
+          <t>{'iterations': 387, 'learning_rate': 0.050418145413024196, 'depth': 4}</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.8077044694841028</v>
+        <v>0.8124569048968405</v>
       </c>
       <c r="F13" t="n">
-        <v>80.30476304547486</v>
+        <v>79.90429286271541</v>
       </c>
       <c r="G13" t="n">
-        <v>48346.44115907176</v>
+        <v>47151.59623247469</v>
       </c>
       <c r="H13" t="n">
-        <v>219.8782416681372</v>
+        <v>217.1441830500524</v>
       </c>
       <c r="I13" t="n">
-        <v>12.36385936959941</v>
+        <v>12.55994412767621</v>
       </c>
       <c r="J13" t="n">
         <v>48168</v>
@@ -1156,7 +1156,7 @@
         <v>9634</v>
       </c>
       <c r="M13" t="n">
-        <v>528.8209052085876</v>
+        <v>479.980541229248</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1183,23 +1183,23 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.7207797756711216</v>
+        <v>0.7202385404301497</v>
       </c>
       <c r="F14" t="n">
-        <v>91.15892603101405</v>
+        <v>94.15652755864645</v>
       </c>
       <c r="G14" t="n">
-        <v>70200.82115129003</v>
+        <v>70336.89710511311</v>
       </c>
       <c r="H14" t="n">
-        <v>264.954375603216</v>
+        <v>265.2110425776293</v>
       </c>
       <c r="I14" t="n">
-        <v>12.36914928556086</v>
+        <v>13.97087436328356</v>
       </c>
       <c r="J14" t="n">
         <v>48168</v>
@@ -1211,7 +1211,7 @@
         <v>9634</v>
       </c>
       <c r="M14" t="n">
-        <v>611.5182316303253</v>
+        <v>546.2579531669617</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>-71.40639971146142</v>
+        <v>-71.64549258964463</v>
       </c>
     </row>
     <row r="15">
@@ -1268,7 +1268,7 @@
         <v>9634</v>
       </c>
       <c r="M15" t="n">
-        <v>65.48641133308411</v>
+        <v>57.59123873710632</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>-64.43932328096163</v>
+        <v>-64.37461566644613</v>
       </c>
     </row>
     <row r="16">
@@ -1297,23 +1297,23 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.001}</t>
+          <t>{'alpha': 0.01, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.001}</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.9453535328427765</v>
+        <v>0.9425512661770665</v>
       </c>
       <c r="F16" t="n">
-        <v>50.09092786740984</v>
+        <v>50.72480469867723</v>
       </c>
       <c r="G16" t="n">
-        <v>13739.07236366808</v>
+        <v>14443.61094603816</v>
       </c>
       <c r="H16" t="n">
-        <v>117.2137891362108</v>
+        <v>120.1815749024706</v>
       </c>
       <c r="I16" t="n">
-        <v>12.79126272979775</v>
+        <v>11.74540094052665</v>
       </c>
       <c r="J16" t="n">
         <v>48168</v>
@@ -1325,7 +1325,7 @@
         <v>9634</v>
       </c>
       <c r="M16" t="n">
-        <v>2273.342207193375</v>
+        <v>1976.045587301254</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>-40.3874711533344</v>
+        <v>-40.12391054232319</v>
       </c>
     </row>
   </sheetData>
